--- a/26아우내영농조합법인 농약 혼용가부표(충).xlsx
+++ b/26아우내영농조합법인 농약 혼용가부표(충).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\농약실험(충)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E10E97C-8C38-4398-A401-AB50D0B58160}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CF0BF6-D228-40F0-87EB-33FF2980BBD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="살충제목록" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4100" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4321" uniqueCount="1223">
   <si>
     <t>순번</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3114,10 +3114,6 @@
   </si>
   <si>
     <t>알투도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>골기퍼</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -4972,6 +4968,329 @@
   </si>
   <si>
     <t>4000배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카벤다짐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디에토펜카브</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3일전 / 3회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carbendazim</t>
+  </si>
+  <si>
+    <t>벤지미다졸계</t>
+  </si>
+  <si>
+    <t>Diethofencarb</t>
+  </si>
+  <si>
+    <t>앤-페닐카바메이트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥시테트라사이클린 칼슘 알킬트리메틸암모늄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트렙토마이신황산염</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아족시스트로빈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>관주 25말로 1동</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>테트라사이클린 안티바이오틱계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oxytetracycline Calcium Alkyltrimethylammonium</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Streptomycin sulfate</t>
+  </si>
+  <si>
+    <t>글루코피라노실계
+(아미노글리코사이드계 항생제)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저독성(어독성3급)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1540배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥솔린산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oxolinc acid</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카복실 에시드계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리옥신디</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>500배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polyoxin D</t>
+  </si>
+  <si>
+    <t>펩틸 피리미딘 뉴클레오사이드계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>마3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저독성(어독성3급)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로사이미돈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Procymidone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디카복시마이드계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코퍼옥시클로라이드</t>
+  </si>
+  <si>
+    <t>코퍼옥시클로라이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디티아논</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>500배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Copper oxychloride</t>
+  </si>
+  <si>
+    <t>Copper oxychloride</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dithianon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기동계</t>
+  </si>
+  <si>
+    <t>무기동계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀴논계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아5</t>
+  </si>
+  <si>
+    <t>아5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>디메토모르프</t>
+  </si>
+  <si>
+    <t>디메토모르프</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dimethomorph</t>
+  </si>
+  <si>
+    <t>시나믹 애시드 아마이드계</t>
+  </si>
+  <si>
+    <t>시나믹 애시드 아마이드계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3일전 / 3회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에트리디아졸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>티오파네이트메틸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>파종기 / 1회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.5말
+(1동 4~5개)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,4-티아디아졸계
+(유기황계)</t>
+  </si>
+  <si>
+    <t>Thiophanate-methyl</t>
+  </si>
+  <si>
+    <t>티오파네이트계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>클로로탈로닐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chlorothalonil </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저독성(어독성1급)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>600배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3일전 / 5회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가스가마이신</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kasugamycin</t>
+  </si>
+  <si>
+    <t>헥소피라노실계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>트리플루미졸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Triflumizole</t>
+  </si>
+  <si>
+    <t>이미다졸계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>폴리옥신비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>골기퍼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polyoxin B</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8043,43 +8362,43 @@
         <v>723</v>
       </c>
       <c r="D1" s="54" t="s">
+        <v>845</v>
+      </c>
+      <c r="E1" s="54" t="s">
         <v>846</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="F1" s="54" t="s">
         <v>847</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="G1" s="54" t="s">
         <v>848</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="H1" s="54" t="s">
         <v>849</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="I1" s="54" t="s">
         <v>850</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="J1" s="54" t="s">
         <v>851</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="K1" s="54" t="s">
         <v>852</v>
       </c>
-      <c r="K1" s="54" t="s">
+      <c r="L1" s="54" t="s">
         <v>853</v>
       </c>
-      <c r="L1" s="54" t="s">
+      <c r="M1" s="54" t="s">
         <v>854</v>
       </c>
-      <c r="M1" s="54" t="s">
+      <c r="N1" s="54" t="s">
         <v>855</v>
       </c>
-      <c r="N1" s="54" t="s">
+      <c r="O1" s="54" t="s">
         <v>856</v>
       </c>
-      <c r="O1" s="54" t="s">
+      <c r="P1" s="54" t="s">
         <v>857</v>
-      </c>
-      <c r="P1" s="54" t="s">
-        <v>858</v>
       </c>
       <c r="Q1" s="54" t="s">
         <v>655</v>
@@ -8097,7 +8416,7 @@
         <v>551</v>
       </c>
       <c r="V1" s="54" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="W1" s="54" t="s">
         <v>1</v>
@@ -8118,10 +8437,10 @@
         <v>553</v>
       </c>
       <c r="AC1" s="54" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AD1" s="55" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AE1" s="54" t="s">
         <v>554</v>
@@ -8130,7 +8449,7 @@
         <v>555</v>
       </c>
       <c r="AG1" s="56" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AH1" s="57"/>
     </row>
@@ -8490,7 +8809,7 @@
         <v>755</v>
       </c>
       <c r="AC5" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AD5" s="6">
         <v>23000</v>
@@ -8786,16 +9105,16 @@
         <v>30</v>
       </c>
       <c r="G9" s="29" t="s">
+        <v>840</v>
+      </c>
+      <c r="H9" s="29" t="s">
         <v>841</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>842</v>
       </c>
       <c r="I9" s="29">
         <v>20</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="29"/>
@@ -8833,13 +9152,13 @@
         <v>607</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AC9" s="5" t="s">
         <v>32</v>
@@ -9011,7 +9330,7 @@
         <v>621</v>
       </c>
       <c r="V11" s="29" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="W11" s="5">
         <v>500</v>
@@ -9023,13 +9342,13 @@
         <v>607</v>
       </c>
       <c r="Z11" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="AB11" s="5" t="s">
         <v>821</v>
-      </c>
-      <c r="AA11" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="AB11" s="5" t="s">
-        <v>822</v>
       </c>
       <c r="AC11" s="5" t="s">
         <v>39</v>
@@ -9109,13 +9428,13 @@
         <v>607</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AA12" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="AB12" s="5" t="s">
         <v>824</v>
-      </c>
-      <c r="AB12" s="5" t="s">
-        <v>825</v>
       </c>
       <c r="AC12" s="5" t="s">
         <v>44</v>
@@ -9195,13 +9514,13 @@
         <v>607</v>
       </c>
       <c r="Z13" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AA13" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="AB13" s="5" t="s">
         <v>824</v>
-      </c>
-      <c r="AB13" s="5" t="s">
-        <v>825</v>
       </c>
       <c r="AC13" s="5" t="s">
         <v>48</v>
@@ -9387,7 +9706,7 @@
         <v>676</v>
       </c>
       <c r="AB15" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="AC15" s="5" t="s">
         <v>57</v>
@@ -9529,7 +9848,7 @@
         <v>30</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="29"/>
@@ -9567,13 +9886,13 @@
         <v>607</v>
       </c>
       <c r="Z17" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="AA17" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="AB17" s="5" t="s">
         <v>821</v>
-      </c>
-      <c r="AA17" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="AB17" s="5" t="s">
-        <v>822</v>
       </c>
       <c r="AC17" s="5" t="s">
         <v>50</v>
@@ -9795,7 +10114,7 @@
         <v>18.66</v>
       </c>
       <c r="J20" s="29" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="29"/>
@@ -9833,13 +10152,13 @@
         <v>607</v>
       </c>
       <c r="Z20" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA20" s="5" t="s">
         <v>578</v>
       </c>
       <c r="AB20" s="5" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AC20" s="5" t="s">
         <v>67</v>
@@ -11089,10 +11408,10 @@
         <v>578</v>
       </c>
       <c r="AB35" s="5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="AC35" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AD35" s="6">
         <v>23000</v>
@@ -11133,7 +11452,7 @@
         <v>8</v>
       </c>
       <c r="J36" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="29"/>
@@ -11171,13 +11490,13 @@
         <v>607</v>
       </c>
       <c r="Z36" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA36" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="AB36" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA36" s="5" t="s">
-        <v>789</v>
-      </c>
-      <c r="AB36" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC36" s="5" t="s">
         <v>7</v>
@@ -11224,7 +11543,7 @@
         <v>10</v>
       </c>
       <c r="J37" s="29" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="29"/>
@@ -11262,13 +11581,13 @@
         <v>607</v>
       </c>
       <c r="Z37" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA37" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AB37" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA37" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AB37" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC37" s="5" t="s">
         <v>7</v>
@@ -11353,13 +11672,13 @@
         <v>607</v>
       </c>
       <c r="Z38" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA38" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AB38" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA38" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AB38" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC38" s="5" t="s">
         <v>118</v>
@@ -11407,7 +11726,7 @@
         <v>10</v>
       </c>
       <c r="J39" s="29" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="29"/>
@@ -11435,13 +11754,13 @@
         <v>607</v>
       </c>
       <c r="Z39" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AA39" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AB39" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AC39" s="5" t="s">
         <v>122</v>
@@ -11567,7 +11886,7 @@
         <v>125</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G41" s="29" t="s">
         <v>497</v>
@@ -11579,7 +11898,7 @@
         <v>7</v>
       </c>
       <c r="J41" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K41" s="5">
         <v>18</v>
@@ -11594,7 +11913,7 @@
         <v>8</v>
       </c>
       <c r="O41" s="29" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="P41" s="29" t="s">
         <v>571</v>
@@ -11627,13 +11946,13 @@
         <v>607</v>
       </c>
       <c r="Z41" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA41" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="AB41" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA41" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="AB41" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC41" s="5" t="s">
         <v>73</v>
@@ -11849,16 +12168,16 @@
         <v>131</v>
       </c>
       <c r="G44" s="29" t="s">
+        <v>794</v>
+      </c>
+      <c r="H44" s="29" t="s">
         <v>795</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>796</v>
       </c>
       <c r="I44" s="29">
         <v>25</v>
       </c>
       <c r="J44" s="29" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="29"/>
@@ -11878,7 +12197,7 @@
         <v>571</v>
       </c>
       <c r="T44" s="29" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="U44" s="29" t="s">
         <v>617</v>
@@ -11896,13 +12215,13 @@
         <v>609</v>
       </c>
       <c r="Z44" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA44" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AB44" s="5" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AC44" s="5" t="s">
         <v>7</v>
@@ -11938,13 +12257,13 @@
         <v>136</v>
       </c>
       <c r="F45" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="G45" s="29" t="s">
         <v>838</v>
       </c>
-      <c r="G45" s="29" t="s">
+      <c r="H45" s="29" t="s">
         <v>839</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>840</v>
       </c>
       <c r="I45" s="29">
         <v>10</v>
@@ -11958,7 +12277,7 @@
       <c r="N45" s="29"/>
       <c r="O45" s="29"/>
       <c r="P45" s="29" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="Q45" s="29" t="s">
         <v>660</v>
@@ -11988,13 +12307,13 @@
         <v>607</v>
       </c>
       <c r="Z45" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA45" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="AB45" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA45" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="AB45" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC45" s="5" t="s">
         <v>73</v>
@@ -12032,16 +12351,16 @@
         <v>30</v>
       </c>
       <c r="G46" s="29" t="s">
+        <v>840</v>
+      </c>
+      <c r="H46" s="29" t="s">
         <v>841</v>
-      </c>
-      <c r="H46" s="29" t="s">
-        <v>842</v>
       </c>
       <c r="I46" s="29">
         <v>20</v>
       </c>
       <c r="J46" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="29"/>
@@ -12079,13 +12398,13 @@
         <v>607</v>
       </c>
       <c r="Z46" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AA46" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB46" s="5" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AC46" s="5" t="s">
         <v>139</v>
@@ -13165,7 +13484,7 @@
         <v>109</v>
       </c>
       <c r="F59" s="51" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G59" s="29" t="s">
         <v>497</v>
@@ -13177,7 +13496,7 @@
         <v>8</v>
       </c>
       <c r="J59" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="29"/>
@@ -13200,7 +13519,7 @@
         <v>571</v>
       </c>
       <c r="U59" s="29" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="V59" s="29" t="s">
         <v>576</v>
@@ -13215,10 +13534,10 @@
         <v>607</v>
       </c>
       <c r="Z59" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA59" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AB59" s="5" t="s">
         <v>719</v>
@@ -13555,7 +13874,7 @@
         <v>30</v>
       </c>
       <c r="F63" s="51" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G63" s="29" t="s">
         <v>497</v>
@@ -13567,7 +13886,7 @@
         <v>8</v>
       </c>
       <c r="J63" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="29"/>
@@ -13590,7 +13909,7 @@
         <v>571</v>
       </c>
       <c r="U63" s="29" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="V63" s="29" t="s">
         <v>576</v>
@@ -13605,13 +13924,13 @@
         <v>607</v>
       </c>
       <c r="Z63" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA63" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AB63" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA63" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AB63" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC63" s="5" t="s">
         <v>7</v>
@@ -13657,7 +13976,7 @@
         <v>8</v>
       </c>
       <c r="J64" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K64" s="5"/>
       <c r="L64" s="29"/>
@@ -13695,13 +14014,13 @@
         <v>609</v>
       </c>
       <c r="Z64" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA64" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="AB64" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA64" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="AB64" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC64" s="5" t="s">
         <v>118</v>
@@ -13747,7 +14066,7 @@
         <v>50</v>
       </c>
       <c r="J65" s="29" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="29"/>
@@ -13773,7 +14092,7 @@
         <v>670</v>
       </c>
       <c r="V65" s="29" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="W65" s="5">
         <v>50</v>
@@ -13785,13 +14104,13 @@
         <v>609</v>
       </c>
       <c r="Z65" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA65" s="5" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AB65" s="5" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AC65" s="5" t="s">
         <v>73</v>
@@ -13833,7 +14152,7 @@
         <v>2.5</v>
       </c>
       <c r="J66" s="29" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="29"/>
@@ -13871,13 +14190,13 @@
         <v>607</v>
       </c>
       <c r="Z66" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA66" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="AB66" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA66" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="AB66" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC66" s="5" t="s">
         <v>15</v>
@@ -13923,7 +14242,7 @@
         <v>8</v>
       </c>
       <c r="J67" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="29"/>
@@ -13961,13 +14280,13 @@
         <v>607</v>
       </c>
       <c r="Z67" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA67" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="AB67" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA67" s="5" t="s">
-        <v>789</v>
-      </c>
-      <c r="AB67" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC67" s="5" t="s">
         <v>7</v>
@@ -14013,7 +14332,7 @@
         <v>10</v>
       </c>
       <c r="J68" s="29" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K68" s="5"/>
       <c r="L68" s="29"/>
@@ -14051,13 +14370,13 @@
         <v>607</v>
       </c>
       <c r="Z68" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA68" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB68" s="5" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AC68" s="5" t="s">
         <v>192</v>
@@ -14103,7 +14422,7 @@
         <v>2.5</v>
       </c>
       <c r="J69" s="29" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="K69" s="5"/>
       <c r="L69" s="29"/>
@@ -14144,10 +14463,10 @@
         <v>579</v>
       </c>
       <c r="AA69" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB69" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AC69" s="5" t="s">
         <v>15</v>
@@ -14231,13 +14550,13 @@
         <v>607</v>
       </c>
       <c r="Z70" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA70" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AB70" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA70" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AB70" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC70" s="5" t="s">
         <v>118</v>
@@ -14283,7 +14602,7 @@
         <v>10</v>
       </c>
       <c r="J71" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K71" s="5"/>
       <c r="L71" s="29"/>
@@ -14321,13 +14640,13 @@
         <v>607</v>
       </c>
       <c r="Z71" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA71" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="AB71" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA71" s="5" t="s">
-        <v>789</v>
-      </c>
-      <c r="AB71" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC71" s="5" t="s">
         <v>480</v>
@@ -14417,10 +14736,10 @@
         <v>565</v>
       </c>
       <c r="AB72" s="5" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AC72" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AD72" s="6">
         <v>23000</v>
@@ -14444,10 +14763,10 @@
         <v>8509</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G73" s="29" t="s">
         <v>537</v>
@@ -14459,22 +14778,22 @@
         <v>24</v>
       </c>
       <c r="J73" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K73" s="5">
         <v>23</v>
       </c>
       <c r="L73" s="29" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="M73" s="29" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="N73" s="29">
         <v>30</v>
       </c>
       <c r="O73" s="29" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="P73" s="29" t="s">
         <v>653</v>
@@ -14507,13 +14826,13 @@
         <v>607</v>
       </c>
       <c r="Z73" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA73" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB73" s="5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AC73" s="5" t="s">
         <v>7</v>
@@ -14547,7 +14866,7 @@
         <v>125</v>
       </c>
       <c r="F74" s="51" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G74" s="29" t="s">
         <v>497</v>
@@ -14559,7 +14878,7 @@
         <v>7</v>
       </c>
       <c r="J74" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K74" s="5">
         <v>18</v>
@@ -14574,7 +14893,7 @@
         <v>8</v>
       </c>
       <c r="O74" s="29" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="P74" s="29" t="s">
         <v>571</v>
@@ -14607,13 +14926,13 @@
         <v>607</v>
       </c>
       <c r="Z74" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA74" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="AB74" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA74" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="AB74" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC74" s="5" t="s">
         <v>15</v>
@@ -14745,22 +15064,22 @@
         <v>10</v>
       </c>
       <c r="J76" s="29" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="L76" s="29" t="s">
+        <v>831</v>
+      </c>
+      <c r="M76" s="29" t="s">
         <v>832</v>
-      </c>
-      <c r="M76" s="29" t="s">
-        <v>833</v>
       </c>
       <c r="N76" s="29">
         <v>5</v>
       </c>
       <c r="O76" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P76" s="29" t="s">
         <v>571</v>
@@ -14781,7 +15100,7 @@
         <v>670</v>
       </c>
       <c r="V76" s="29" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="W76" s="5">
         <v>250</v>
@@ -14793,13 +15112,13 @@
         <v>607</v>
       </c>
       <c r="Z76" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA76" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AB76" s="5" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AC76" s="5" t="s">
         <v>207</v>
@@ -14832,16 +15151,16 @@
         <v>131</v>
       </c>
       <c r="G77" s="29" t="s">
+        <v>794</v>
+      </c>
+      <c r="H77" s="29" t="s">
         <v>795</v>
-      </c>
-      <c r="H77" s="29" t="s">
-        <v>796</v>
       </c>
       <c r="I77" s="29">
         <v>25</v>
       </c>
       <c r="J77" s="29" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="K77" s="5"/>
       <c r="L77" s="29"/>
@@ -14861,7 +15180,7 @@
         <v>571</v>
       </c>
       <c r="T77" s="29" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="U77" s="29" t="s">
         <v>617</v>
@@ -14879,13 +15198,13 @@
         <v>609</v>
       </c>
       <c r="Z77" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA77" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AB77" s="5" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AC77" s="5" t="s">
         <v>15</v>
@@ -15012,16 +15331,16 @@
         <v>30</v>
       </c>
       <c r="G79" s="29" t="s">
+        <v>818</v>
+      </c>
+      <c r="H79" s="29" t="s">
         <v>819</v>
-      </c>
-      <c r="H79" s="29" t="s">
-        <v>820</v>
       </c>
       <c r="I79" s="29">
         <v>8</v>
       </c>
       <c r="J79" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K79" s="5"/>
       <c r="L79" s="29"/>
@@ -15059,13 +15378,13 @@
         <v>607</v>
       </c>
       <c r="Z79" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AA79" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB79" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AC79" s="5" t="s">
         <v>7</v>
@@ -15102,16 +15421,16 @@
         <v>30</v>
       </c>
       <c r="G80" s="29" t="s">
+        <v>840</v>
+      </c>
+      <c r="H80" s="29" t="s">
         <v>841</v>
-      </c>
-      <c r="H80" s="29" t="s">
-        <v>842</v>
       </c>
       <c r="I80" s="29">
         <v>20</v>
       </c>
       <c r="J80" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K80" s="5"/>
       <c r="L80" s="29"/>
@@ -15149,13 +15468,13 @@
         <v>607</v>
       </c>
       <c r="Z80" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AA80" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB80" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AC80" s="5" t="s">
         <v>15</v>
@@ -16165,7 +16484,7 @@
         <v>20</v>
       </c>
       <c r="J92" s="29" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K92" s="5"/>
       <c r="L92" s="29"/>
@@ -16203,13 +16522,13 @@
         <v>607</v>
       </c>
       <c r="Z92" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA92" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AB92" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA92" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AB92" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC92" s="5" t="s">
         <v>122</v>
@@ -16333,7 +16652,7 @@
         <v>125</v>
       </c>
       <c r="F94" s="51" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G94" s="29" t="s">
         <v>497</v>
@@ -16345,7 +16664,7 @@
         <v>7</v>
       </c>
       <c r="J94" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K94" s="5">
         <v>18</v>
@@ -16360,7 +16679,7 @@
         <v>8</v>
       </c>
       <c r="O94" s="29" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="P94" s="29" t="s">
         <v>571</v>
@@ -16393,13 +16712,13 @@
         <v>607</v>
       </c>
       <c r="Z94" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA94" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="AB94" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA94" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="AB94" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC94" s="5" t="s">
         <v>15</v>
@@ -16891,7 +17210,7 @@
         <v>20</v>
       </c>
       <c r="J100" s="29" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K100" s="5"/>
       <c r="L100" s="29"/>
@@ -16929,13 +17248,13 @@
         <v>607</v>
       </c>
       <c r="Z100" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA100" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AB100" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA100" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AB100" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC100" s="5" t="s">
         <v>249</v>
@@ -17645,7 +17964,7 @@
         <v>8</v>
       </c>
       <c r="J109" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K109" s="5"/>
       <c r="L109" s="29"/>
@@ -17683,13 +18002,13 @@
         <v>607</v>
       </c>
       <c r="Z109" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA109" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="AB109" s="5" t="s">
         <v>789</v>
-      </c>
-      <c r="AB109" s="5" t="s">
-        <v>790</v>
       </c>
       <c r="AC109" s="5" t="s">
         <v>263</v>
@@ -17735,7 +18054,7 @@
         <v>10</v>
       </c>
       <c r="J110" s="29" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K110" s="5"/>
       <c r="L110" s="29"/>
@@ -17773,13 +18092,13 @@
         <v>607</v>
       </c>
       <c r="Z110" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA110" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="AB110" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA110" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="AB110" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC110" s="5" t="s">
         <v>7</v>
@@ -17925,7 +18244,7 @@
         <v>10</v>
       </c>
       <c r="J112" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K112" s="5"/>
       <c r="L112" s="29"/>
@@ -17963,13 +18282,13 @@
         <v>607</v>
       </c>
       <c r="Z112" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="AA112" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="AB112" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="AA112" s="5" t="s">
-        <v>789</v>
-      </c>
-      <c r="AB112" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="AC112" s="5" t="s">
         <v>480</v>
@@ -18952,16 +19271,16 @@
         <v>30</v>
       </c>
       <c r="G124" s="29" t="s">
+        <v>840</v>
+      </c>
+      <c r="H124" s="29" t="s">
         <v>841</v>
-      </c>
-      <c r="H124" s="29" t="s">
-        <v>842</v>
       </c>
       <c r="I124" s="29">
         <v>20</v>
       </c>
       <c r="J124" s="29" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K124" s="5"/>
       <c r="L124" s="29"/>
@@ -18999,13 +19318,13 @@
         <v>607</v>
       </c>
       <c r="Z124" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AA124" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AB124" s="5" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AC124" s="5" t="s">
         <v>139</v>
@@ -19417,15 +19736,15 @@
     <col min="4" max="4" width="7.125" style="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.625" style="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.75" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.75" style="36" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.375" style="36" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.25" style="36" customWidth="1"/>
     <col min="9" max="9" width="9" style="36" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26.25" style="36" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.75" style="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="36" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.875" style="36" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.75" style="36" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" style="36" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.375" style="36" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24.375" style="36" customWidth="1"/>
     <col min="16" max="16" width="12.125" style="36" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.75" style="36" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.875" style="36" bestFit="1" customWidth="1"/>
@@ -19457,46 +19776,46 @@
         <v>723</v>
       </c>
       <c r="D1" s="54" t="s">
+        <v>845</v>
+      </c>
+      <c r="E1" s="54" t="s">
         <v>846</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="F1" s="54" t="s">
         <v>847</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="G1" s="54" t="s">
         <v>848</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="H1" s="54" t="s">
         <v>849</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="I1" s="54" t="s">
         <v>850</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="J1" s="54" t="s">
         <v>851</v>
       </c>
-      <c r="J1" s="54" t="s">
+      <c r="K1" s="54" t="s">
         <v>852</v>
       </c>
-      <c r="K1" s="54" t="s">
+      <c r="L1" s="54" t="s">
         <v>853</v>
       </c>
-      <c r="L1" s="54" t="s">
+      <c r="M1" s="54" t="s">
         <v>854</v>
       </c>
-      <c r="M1" s="54" t="s">
+      <c r="N1" s="54" t="s">
         <v>855</v>
       </c>
-      <c r="N1" s="54" t="s">
+      <c r="O1" s="54" t="s">
         <v>856</v>
       </c>
-      <c r="O1" s="54" t="s">
-        <v>857</v>
-      </c>
       <c r="P1" s="54" t="s">
+        <v>947</v>
+      </c>
+      <c r="Q1" s="54" t="s">
         <v>948</v>
-      </c>
-      <c r="Q1" s="54" t="s">
-        <v>949</v>
       </c>
       <c r="R1" s="54" t="s">
         <v>580</v>
@@ -19511,7 +19830,7 @@
         <v>551</v>
       </c>
       <c r="V1" s="54" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="W1" s="54" t="s">
         <v>1</v>
@@ -19532,10 +19851,10 @@
         <v>553</v>
       </c>
       <c r="AC1" s="54" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AD1" s="55" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AE1" s="54" t="s">
         <v>554</v>
@@ -19544,7 +19863,7 @@
         <v>555</v>
       </c>
       <c r="AG1" s="56" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AH1" s="57"/>
     </row>
@@ -19568,16 +19887,16 @@
         <v>422</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I2" s="28">
         <v>26.5</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="28"/>
@@ -19585,7 +19904,7 @@
       <c r="N2" s="28"/>
       <c r="O2" s="28"/>
       <c r="P2" s="28" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q2" s="28"/>
       <c r="R2" s="28" t="s">
@@ -19595,13 +19914,13 @@
         <v>571</v>
       </c>
       <c r="T2" s="28" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="U2" s="28" t="s">
         <v>591</v>
       </c>
       <c r="V2" s="28" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="W2" s="12" t="s">
         <v>290</v>
@@ -19613,13 +19932,13 @@
         <v>607</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="AA2" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="AB2" s="12" t="s">
         <v>866</v>
-      </c>
-      <c r="AB2" s="12" t="s">
-        <v>867</v>
       </c>
       <c r="AC2" s="12" t="s">
         <v>7</v>
@@ -19647,23 +19966,57 @@
       <c r="E3" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
+      <c r="F3" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I3" s="29">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="J3" s="29" t="s">
+        <v>1184</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="L3" s="29" t="s">
+        <v>1211</v>
+      </c>
+      <c r="M3" s="29" t="s">
+        <v>1212</v>
+      </c>
+      <c r="N3" s="29">
+        <v>5.75</v>
+      </c>
+      <c r="O3" s="29" t="s">
+        <v>1213</v>
+      </c>
+      <c r="P3" s="29" t="s">
+        <v>972</v>
+      </c>
+      <c r="Q3" s="29" t="s">
+        <v>889</v>
+      </c>
+      <c r="R3" s="29" t="s">
+        <v>569</v>
+      </c>
+      <c r="S3" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T3" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U3" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V3" s="29" t="s">
+        <v>576</v>
+      </c>
       <c r="W3" s="5" t="s">
         <v>316</v>
       </c>
@@ -19673,9 +20026,15 @@
       <c r="Y3" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
+      <c r="Z3" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>1172</v>
+      </c>
       <c r="AC3" s="5" t="s">
         <v>122</v>
       </c>
@@ -19706,23 +20065,57 @@
       <c r="E4" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
+      <c r="F4" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I4" s="29">
+        <v>10</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>1202</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>1199</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>1203</v>
+      </c>
+      <c r="N4" s="29">
+        <v>55</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>1204</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>895</v>
+      </c>
+      <c r="Q4" s="29" t="s">
+        <v>928</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="S4" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V4" s="29" t="s">
+        <v>593</v>
+      </c>
       <c r="W4" s="5" t="s">
         <v>395</v>
       </c>
@@ -19732,10 +20125,18 @@
       <c r="Y4" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
+      <c r="Z4" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>1201</v>
+      </c>
       <c r="AD4" s="6">
         <v>14000</v>
       </c>
@@ -19752,8 +20153,8 @@
       <c r="B5" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>780</v>
+      <c r="C5" s="52" t="s">
+        <v>1220</v>
       </c>
       <c r="D5" s="41"/>
       <c r="E5" s="5" t="s">
@@ -19777,7 +20178,7 @@
       <c r="U5" s="29"/>
       <c r="V5" s="29"/>
       <c r="W5" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="X5" s="5"/>
       <c r="Y5" s="5"/>
@@ -19800,28 +20201,28 @@
         <v>401</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D6" s="41">
         <v>8954</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G6" s="29" t="s">
         <v>1015</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G6" s="29" t="s">
+      <c r="H6" s="29" t="s">
         <v>1016</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>1017</v>
       </c>
       <c r="I6" s="29">
         <v>20</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="29"/>
@@ -19829,7 +20230,7 @@
       <c r="N6" s="29"/>
       <c r="O6" s="29"/>
       <c r="P6" s="29" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="Q6" s="29" t="s">
         <v>571</v>
@@ -19841,16 +20242,16 @@
         <v>571</v>
       </c>
       <c r="T6" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U6" s="29" t="s">
         <v>591</v>
       </c>
       <c r="V6" s="29" t="s">
+        <v>1017</v>
+      </c>
+      <c r="W6" s="5" t="s">
         <v>1018</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>1019</v>
       </c>
       <c r="X6" s="5" t="s">
         <v>667</v>
@@ -19859,16 +20260,16 @@
         <v>607</v>
       </c>
       <c r="Z6" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="AC6" s="5" t="s">
         <v>1020</v>
-      </c>
-      <c r="AA6" s="5" t="s">
-        <v>952</v>
-      </c>
-      <c r="AB6" s="5" t="s">
-        <v>1009</v>
-      </c>
-      <c r="AC6" s="5" t="s">
-        <v>1021</v>
       </c>
       <c r="AD6" s="6">
         <v>25000</v>
@@ -19885,7 +20286,7 @@
         <v>305</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D7" s="41">
         <v>993</v>
@@ -19893,25 +20294,59 @@
       <c r="E7" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
+      <c r="F7" s="5" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I7" s="29">
+        <v>25</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>1147</v>
+      </c>
+      <c r="N7" s="29">
+        <v>25</v>
+      </c>
+      <c r="O7" s="29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="P7" s="29" t="s">
+        <v>928</v>
+      </c>
+      <c r="Q7" s="29" t="s">
+        <v>928</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>569</v>
+      </c>
+      <c r="S7" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T7" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U7" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V7" s="29" t="s">
+        <v>576</v>
+      </c>
       <c r="W7" s="5" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="X7" s="5" t="s">
         <v>666</v>
@@ -19919,9 +20354,15 @@
       <c r="Y7" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
+      <c r="Z7" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AB7" s="5" t="s">
+        <v>1143</v>
+      </c>
       <c r="AC7" s="5" t="s">
         <v>413</v>
       </c>
@@ -19952,23 +20393,47 @@
       <c r="E8" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
+      <c r="F8" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>1206</v>
+      </c>
+      <c r="I8" s="29">
+        <v>75</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>1110</v>
+      </c>
       <c r="K8" s="5"/>
       <c r="L8" s="29"/>
       <c r="M8" s="29"/>
       <c r="N8" s="29"/>
       <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
+      <c r="P8" s="29" t="s">
+        <v>972</v>
+      </c>
+      <c r="Q8" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="R8" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="S8" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T8" s="29" t="s">
+        <v>797</v>
+      </c>
+      <c r="U8" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V8" s="29" t="s">
+        <v>714</v>
+      </c>
       <c r="W8" s="5" t="s">
         <v>242</v>
       </c>
@@ -19978,9 +20443,15 @@
       <c r="Y8" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
+      <c r="Z8" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AB8" s="5" t="s">
+        <v>1208</v>
+      </c>
       <c r="AC8" s="5" t="s">
         <v>462</v>
       </c>
@@ -20008,19 +20479,19 @@
         <v>320</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G9" s="29" t="s">
         <v>1109</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>1110</v>
-      </c>
       <c r="H9" s="29" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="I9" s="29">
         <v>53</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="29"/>
@@ -20028,7 +20499,7 @@
       <c r="N9" s="29"/>
       <c r="O9" s="29"/>
       <c r="P9" s="29" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="Q9" s="29" t="s">
         <v>571</v>
@@ -20040,7 +20511,7 @@
         <v>571</v>
       </c>
       <c r="T9" s="29" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="U9" s="29" t="s">
         <v>591</v>
@@ -20061,10 +20532,10 @@
         <v>668</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AC9" s="5" t="s">
         <v>7</v>
@@ -20096,23 +20567,57 @@
       <c r="E10" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
+      <c r="F10" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I10" s="29">
+        <v>42</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>1185</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M10" s="29" t="s">
+        <v>1183</v>
+      </c>
+      <c r="N10" s="29">
+        <v>13</v>
+      </c>
+      <c r="O10" s="29" t="s">
+        <v>1186</v>
+      </c>
+      <c r="P10" s="29" t="s">
+        <v>972</v>
+      </c>
+      <c r="Q10" s="29" t="s">
+        <v>972</v>
+      </c>
+      <c r="R10" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="S10" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T10" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U10" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V10" s="29" t="s">
+        <v>631</v>
+      </c>
       <c r="W10" s="5" t="s">
         <v>242</v>
       </c>
@@ -20122,9 +20627,13 @@
       <c r="Y10" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z10" s="5"/>
+      <c r="Z10" s="5" t="s">
+        <v>579</v>
+      </c>
       <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
+      <c r="AB10" s="5" t="s">
+        <v>1180</v>
+      </c>
       <c r="AC10" s="5" t="s">
         <v>21</v>
       </c>
@@ -20147,49 +20656,49 @@
         <v>420</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D11" s="41">
         <v>3146</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="I11" s="29">
         <v>21.3</v>
       </c>
       <c r="J11" s="29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="L11" s="29" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M11" s="29" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N11" s="29">
         <v>21.3</v>
       </c>
       <c r="O11" s="29" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="P11" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q11" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="R11" s="29" t="s">
         <v>571</v>
@@ -20198,7 +20707,7 @@
         <v>569</v>
       </c>
       <c r="T11" s="29" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="U11" s="29" t="s">
         <v>591</v>
@@ -20207,7 +20716,7 @@
         <v>629</v>
       </c>
       <c r="W11" s="5" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="X11" s="5" t="s">
         <v>667</v>
@@ -20216,25 +20725,25 @@
         <v>607</v>
       </c>
       <c r="Z11" s="5" t="s">
+        <v>979</v>
+      </c>
+      <c r="AA11" s="5" t="s">
         <v>980</v>
       </c>
-      <c r="AA11" s="5" t="s">
+      <c r="AB11" s="5" t="s">
         <v>981</v>
       </c>
-      <c r="AB11" s="5" t="s">
+      <c r="AC11" s="5" t="s">
         <v>982</v>
-      </c>
-      <c r="AC11" s="5" t="s">
-        <v>983</v>
       </c>
       <c r="AD11" s="6">
         <v>18500</v>
       </c>
       <c r="AE11" s="7" t="s">
+        <v>989</v>
+      </c>
+      <c r="AF11" s="7" t="s">
         <v>990</v>
-      </c>
-      <c r="AF11" s="7" t="s">
-        <v>991</v>
       </c>
       <c r="AG11" s="8"/>
     </row>
@@ -20255,19 +20764,19 @@
         <v>329</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G12" s="29" t="s">
         <v>1057</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="H12" s="29" t="s">
         <v>1058</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>1059</v>
       </c>
       <c r="I12" s="29">
         <v>13.5</v>
       </c>
       <c r="J12" s="29" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="29"/>
@@ -20275,7 +20784,7 @@
       <c r="N12" s="29"/>
       <c r="O12" s="29"/>
       <c r="P12" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q12" s="29" t="s">
         <v>571</v>
@@ -20287,7 +20796,7 @@
         <v>571</v>
       </c>
       <c r="T12" s="29" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="U12" s="29" t="s">
         <v>591</v>
@@ -20305,13 +20814,13 @@
         <v>607</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AA12" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AC12" s="5" t="s">
         <v>7</v>
@@ -20344,19 +20853,19 @@
         <v>294</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G13" s="29" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H13" s="29" t="s">
         <v>1012</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>1013</v>
       </c>
       <c r="I13" s="29">
         <v>18.350000000000001</v>
       </c>
       <c r="J13" s="29" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="29"/>
@@ -20364,7 +20873,7 @@
       <c r="N13" s="29"/>
       <c r="O13" s="29"/>
       <c r="P13" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q13" s="29" t="s">
         <v>571</v>
@@ -20376,7 +20885,7 @@
         <v>571</v>
       </c>
       <c r="T13" s="29" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="U13" s="29" t="s">
         <v>591</v>
@@ -20397,10 +20906,10 @@
         <v>564</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="AB13" s="5" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="AC13" s="5" t="s">
         <v>7</v>
@@ -20436,16 +20945,16 @@
         <v>42</v>
       </c>
       <c r="G14" s="29" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H14" s="29" t="s">
         <v>1012</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>1013</v>
       </c>
       <c r="I14" s="29">
         <v>18.350000000000001</v>
       </c>
       <c r="J14" s="29" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="29"/>
@@ -20453,7 +20962,7 @@
       <c r="N14" s="29"/>
       <c r="O14" s="29"/>
       <c r="P14" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q14" s="29" t="s">
         <v>571</v>
@@ -20465,7 +20974,7 @@
         <v>571</v>
       </c>
       <c r="T14" s="29" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="U14" s="29" t="s">
         <v>591</v>
@@ -20489,7 +20998,7 @@
         <v>676</v>
       </c>
       <c r="AB14" s="5" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="AC14" s="5" t="s">
         <v>7</v>
@@ -20510,52 +21019,52 @@
         <v>4</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D15" s="41">
         <v>3040</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H15" s="29" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="I15" s="29">
         <v>4.5999999999999996</v>
       </c>
       <c r="J15" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="L15" s="29" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="M15" s="29" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="N15" s="29">
         <v>8.3000000000000007</v>
       </c>
       <c r="O15" s="29" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="P15" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q15" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="R15" s="29" t="s">
         <v>569</v>
@@ -20564,7 +21073,7 @@
         <v>569</v>
       </c>
       <c r="T15" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U15" s="29" t="s">
         <v>591</v>
@@ -20573,7 +21082,7 @@
         <v>593</v>
       </c>
       <c r="W15" s="5" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="X15" s="5" t="s">
         <v>667</v>
@@ -20582,25 +21091,25 @@
         <v>607</v>
       </c>
       <c r="Z15" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="AA15" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB15" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AC15" s="5" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="AD15" s="6">
         <v>29000</v>
       </c>
       <c r="AE15" s="7" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="AF15" s="7" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="AG15" s="8"/>
     </row>
@@ -20621,19 +21130,19 @@
         <v>334</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H16" s="29" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="I16" s="29">
         <v>10</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="29"/>
@@ -20641,7 +21150,7 @@
       <c r="N16" s="29"/>
       <c r="O16" s="29"/>
       <c r="P16" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q16" s="29" t="s">
         <v>571</v>
@@ -20653,7 +21162,7 @@
         <v>569</v>
       </c>
       <c r="T16" s="29" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="U16" s="29" t="s">
         <v>591</v>
@@ -20674,10 +21183,10 @@
         <v>579</v>
       </c>
       <c r="AA16" s="5" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="AB16" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AC16" s="5" t="s">
         <v>335</v>
@@ -20713,16 +21222,16 @@
         <v>329</v>
       </c>
       <c r="G17" s="29" t="s">
+        <v>872</v>
+      </c>
+      <c r="H17" s="29" t="s">
         <v>873</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>874</v>
       </c>
       <c r="I17" s="29">
         <v>10</v>
       </c>
       <c r="J17" s="29" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="29"/>
@@ -20730,7 +21239,7 @@
       <c r="N17" s="29"/>
       <c r="O17" s="29"/>
       <c r="P17" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q17" s="29" t="s">
         <v>571</v>
@@ -20742,7 +21251,7 @@
         <v>571</v>
       </c>
       <c r="T17" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U17" s="29" t="s">
         <v>591</v>
@@ -20760,13 +21269,13 @@
         <v>607</v>
       </c>
       <c r="Z17" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="AA17" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="AA17" s="5" t="s">
+      <c r="AB17" s="5" t="s">
         <v>870</v>
-      </c>
-      <c r="AB17" s="5" t="s">
-        <v>871</v>
       </c>
       <c r="AC17" s="5" t="s">
         <v>15</v>
@@ -20799,40 +21308,40 @@
         <v>406</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G18" s="29" t="s">
+        <v>944</v>
+      </c>
+      <c r="H18" s="29" t="s">
         <v>945</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>946</v>
       </c>
       <c r="I18" s="29">
         <v>8</v>
       </c>
       <c r="J18" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K18" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>943</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>944</v>
-      </c>
       <c r="M18" s="29" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="N18" s="29">
         <v>9.1</v>
       </c>
       <c r="O18" s="29" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="P18" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q18" s="29" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="R18" s="29" t="s">
         <v>571</v>
@@ -20841,7 +21350,7 @@
         <v>571</v>
       </c>
       <c r="T18" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U18" s="29" t="s">
         <v>591</v>
@@ -20859,13 +21368,13 @@
         <v>607</v>
       </c>
       <c r="Z18" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AA18" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AB18" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AC18" s="5" t="s">
         <v>122</v>
@@ -20898,40 +21407,40 @@
         <v>428</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G19" s="29" t="s">
+        <v>944</v>
+      </c>
+      <c r="H19" s="29" t="s">
         <v>945</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>946</v>
       </c>
       <c r="I19" s="29">
         <v>8</v>
       </c>
       <c r="J19" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K19" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="L19" s="29" t="s">
         <v>943</v>
       </c>
-      <c r="L19" s="29" t="s">
-        <v>944</v>
-      </c>
       <c r="M19" s="29" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="N19" s="29">
         <v>9.1</v>
       </c>
       <c r="O19" s="29" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="P19" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q19" s="29" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="R19" s="29" t="s">
         <v>571</v>
@@ -20940,7 +21449,7 @@
         <v>571</v>
       </c>
       <c r="T19" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U19" s="29" t="s">
         <v>591</v>
@@ -20958,13 +21467,13 @@
         <v>607</v>
       </c>
       <c r="Z19" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AA19" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AB19" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AC19" s="5" t="s">
         <v>122</v>
@@ -20997,40 +21506,40 @@
         <v>406</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G20" s="29" t="s">
+        <v>944</v>
+      </c>
+      <c r="H20" s="29" t="s">
         <v>945</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>946</v>
       </c>
       <c r="I20" s="29">
         <v>8</v>
       </c>
       <c r="J20" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K20" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="L20" s="29" t="s">
         <v>943</v>
       </c>
-      <c r="L20" s="29" t="s">
-        <v>944</v>
-      </c>
       <c r="M20" s="29" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="N20" s="29">
         <v>9.1</v>
       </c>
       <c r="O20" s="29" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="P20" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q20" s="29" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="R20" s="29" t="s">
         <v>571</v>
@@ -21039,7 +21548,7 @@
         <v>571</v>
       </c>
       <c r="T20" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U20" s="29" t="s">
         <v>591</v>
@@ -21057,16 +21566,16 @@
         <v>607</v>
       </c>
       <c r="Z20" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AA20" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="AB20" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="AB20" s="5" t="s">
+      <c r="AC20" s="5" t="s">
         <v>954</v>
-      </c>
-      <c r="AC20" s="5" t="s">
-        <v>955</v>
       </c>
       <c r="AD20" s="6">
         <v>18500</v>
@@ -21096,19 +21605,19 @@
         <v>311</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G21" s="29" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H21" s="29" t="s">
         <v>1016</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>1017</v>
       </c>
       <c r="I21" s="29">
         <v>20</v>
       </c>
       <c r="J21" s="29" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="29"/>
@@ -21116,7 +21625,7 @@
       <c r="N21" s="29"/>
       <c r="O21" s="29"/>
       <c r="P21" s="29" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="Q21" s="29" t="s">
         <v>571</v>
@@ -21128,7 +21637,7 @@
         <v>571</v>
       </c>
       <c r="T21" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U21" s="29" t="s">
         <v>591</v>
@@ -21149,10 +21658,10 @@
         <v>579</v>
       </c>
       <c r="AA21" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AB21" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AC21" s="5" t="s">
         <v>122</v>
@@ -21183,19 +21692,19 @@
         <v>311</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G22" s="29" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H22" s="29" t="s">
         <v>1016</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>1017</v>
       </c>
       <c r="I22" s="29">
         <v>20</v>
       </c>
       <c r="J22" s="29" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="29"/>
@@ -21203,7 +21712,7 @@
       <c r="N22" s="29"/>
       <c r="O22" s="29"/>
       <c r="P22" s="29" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="Q22" s="29" t="s">
         <v>571</v>
@@ -21215,7 +21724,7 @@
         <v>571</v>
       </c>
       <c r="T22" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U22" s="29" t="s">
         <v>591</v>
@@ -21236,10 +21745,10 @@
         <v>579</v>
       </c>
       <c r="AA22" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AB22" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AC22" s="5" t="s">
         <v>122</v>
@@ -21261,7 +21770,7 @@
         <v>401</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D23" s="41">
         <v>1353</v>
@@ -21270,19 +21779,19 @@
         <v>311</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G23" s="29" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H23" s="29" t="s">
         <v>1016</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>1017</v>
       </c>
       <c r="I23" s="29">
         <v>20</v>
       </c>
       <c r="J23" s="29" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="29"/>
@@ -21290,7 +21799,7 @@
       <c r="N23" s="29"/>
       <c r="O23" s="29"/>
       <c r="P23" s="29" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="Q23" s="29" t="s">
         <v>571</v>
@@ -21305,13 +21814,13 @@
         <v>571</v>
       </c>
       <c r="U23" s="29" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="V23" s="29" t="s">
         <v>593</v>
       </c>
       <c r="W23" s="5" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="X23" s="5" t="s">
         <v>666</v>
@@ -21326,10 +21835,10 @@
         <v>679</v>
       </c>
       <c r="AB23" s="5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="AC23" s="5" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AD23" s="6">
         <v>14000</v>
@@ -21355,19 +21864,19 @@
         <v>432</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="G24" s="29" t="s">
         <v>971</v>
       </c>
-      <c r="G24" s="29" t="s">
-        <v>972</v>
-      </c>
       <c r="H24" s="29" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="I24" s="29">
         <v>20</v>
       </c>
       <c r="J24" s="29" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="29"/>
@@ -21375,7 +21884,7 @@
       <c r="N24" s="29"/>
       <c r="O24" s="29"/>
       <c r="P24" s="29" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="Q24" s="29" t="s">
         <v>571</v>
@@ -21387,7 +21896,7 @@
         <v>571</v>
       </c>
       <c r="T24" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U24" s="29" t="s">
         <v>615</v>
@@ -21405,13 +21914,13 @@
         <v>607</v>
       </c>
       <c r="Z24" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AA24" s="5" t="s">
         <v>688</v>
       </c>
       <c r="AB24" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="AC24" s="5" t="s">
         <v>21</v>
@@ -21444,19 +21953,19 @@
         <v>294</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="I25" s="29">
         <v>12.57</v>
       </c>
       <c r="J25" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="29"/>
@@ -21464,7 +21973,7 @@
       <c r="N25" s="29"/>
       <c r="O25" s="29"/>
       <c r="P25" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q25" s="29" t="s">
         <v>571</v>
@@ -21476,7 +21985,7 @@
         <v>571</v>
       </c>
       <c r="T25" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U25" s="29" t="s">
         <v>615</v>
@@ -21485,7 +21994,7 @@
         <v>635</v>
       </c>
       <c r="W25" s="5" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="X25" s="5" t="s">
         <v>667</v>
@@ -21494,13 +22003,13 @@
         <v>607</v>
       </c>
       <c r="Z25" s="5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="AA25" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB25" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AC25" s="5" t="s">
         <v>122</v>
@@ -21533,40 +22042,40 @@
         <v>398</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G26" s="29" t="s">
+        <v>944</v>
+      </c>
+      <c r="H26" s="29" t="s">
         <v>945</v>
-      </c>
-      <c r="H26" s="29" t="s">
-        <v>946</v>
       </c>
       <c r="I26" s="29">
         <v>4</v>
       </c>
       <c r="J26" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K26" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="L26" s="29" t="s">
         <v>1088</v>
       </c>
-      <c r="L26" s="29" t="s">
+      <c r="M26" s="29" t="s">
         <v>1089</v>
-      </c>
-      <c r="M26" s="29" t="s">
-        <v>1090</v>
       </c>
       <c r="N26" s="29">
         <v>4</v>
       </c>
       <c r="O26" s="29" t="s">
+        <v>1090</v>
+      </c>
+      <c r="P26" s="29" t="s">
+        <v>929</v>
+      </c>
+      <c r="Q26" s="29" t="s">
         <v>1091</v>
-      </c>
-      <c r="P26" s="29" t="s">
-        <v>930</v>
-      </c>
-      <c r="Q26" s="29" t="s">
-        <v>1092</v>
       </c>
       <c r="R26" s="29" t="s">
         <v>569</v>
@@ -21575,7 +22084,7 @@
         <v>571</v>
       </c>
       <c r="T26" s="29" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="U26" s="29" t="s">
         <v>591</v>
@@ -21596,13 +22105,13 @@
         <v>564</v>
       </c>
       <c r="AA26" s="5" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AB26" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AC26" s="5" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="AD26" s="6">
         <v>30000</v>
@@ -21628,40 +22137,40 @@
         <v>339</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G27" s="29" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="I27" s="29">
         <v>3</v>
       </c>
       <c r="J27" s="29" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="L27" s="29" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="M27" s="29" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="N27" s="29">
         <v>5</v>
       </c>
       <c r="O27" s="29" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="P27" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q27" s="29" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="R27" s="29" t="s">
         <v>569</v>
@@ -21670,7 +22179,7 @@
         <v>571</v>
       </c>
       <c r="T27" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U27" s="29" t="s">
         <v>591</v>
@@ -21688,13 +22197,13 @@
         <v>607</v>
       </c>
       <c r="Z27" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AA27" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB27" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AC27" s="5" t="s">
         <v>122</v>
@@ -21726,23 +22235,47 @@
       <c r="E28" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
+      <c r="F28" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I28" s="29">
+        <v>50</v>
+      </c>
+      <c r="J28" s="29" t="s">
+        <v>1175</v>
+      </c>
       <c r="K28" s="5"/>
       <c r="L28" s="29"/>
       <c r="M28" s="29"/>
       <c r="N28" s="29"/>
       <c r="O28" s="29"/>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
+      <c r="P28" s="29" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Q28" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="R28" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="S28" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T28" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U28" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V28" s="29" t="s">
+        <v>576</v>
+      </c>
       <c r="W28" s="5" t="s">
         <v>412</v>
       </c>
@@ -21752,9 +22285,15 @@
       <c r="Y28" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z28" s="5"/>
-      <c r="AA28" s="5"/>
-      <c r="AB28" s="5"/>
+      <c r="Z28" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AA28" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="AB28" s="5" t="s">
+        <v>1172</v>
+      </c>
       <c r="AC28" s="5" t="s">
         <v>413</v>
       </c>
@@ -21786,19 +22325,19 @@
         <v>343</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G29" s="29" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H29" s="29" t="s">
         <v>1085</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>1086</v>
       </c>
       <c r="I29" s="29">
         <v>1.9</v>
       </c>
       <c r="J29" s="29" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="29"/>
@@ -21806,7 +22345,7 @@
       <c r="N29" s="29"/>
       <c r="O29" s="29"/>
       <c r="P29" s="29" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="Q29" s="29" t="s">
         <v>571</v>
@@ -21818,7 +22357,7 @@
         <v>571</v>
       </c>
       <c r="T29" s="29" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="U29" s="29" t="s">
         <v>591</v>
@@ -21842,7 +22381,7 @@
         <v>679</v>
       </c>
       <c r="AB29" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AC29" s="5" t="s">
         <v>344</v>
@@ -21874,23 +22413,57 @@
       <c r="E30" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
+      <c r="F30" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H30" s="29" t="s">
+        <v>1156</v>
+      </c>
+      <c r="I30" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>1155</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>1152</v>
+      </c>
+      <c r="M30" s="29" t="s">
+        <v>1157</v>
+      </c>
+      <c r="N30" s="29">
+        <v>18.8</v>
+      </c>
+      <c r="O30" s="29" t="s">
+        <v>1158</v>
+      </c>
+      <c r="P30" s="29" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q30" s="29" t="s">
+        <v>889</v>
+      </c>
+      <c r="R30" s="29" t="s">
+        <v>569</v>
+      </c>
+      <c r="S30" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T30" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U30" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V30" s="29" t="s">
+        <v>706</v>
+      </c>
       <c r="W30" s="5" t="s">
         <v>307</v>
       </c>
@@ -21900,9 +22473,15 @@
       <c r="Y30" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z30" s="5"/>
-      <c r="AA30" s="5"/>
-      <c r="AB30" s="5"/>
+      <c r="Z30" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AA30" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AB30" s="5" t="s">
+        <v>1160</v>
+      </c>
       <c r="AC30" s="5" t="s">
         <v>386</v>
       </c>
@@ -21934,19 +22513,19 @@
         <v>400</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G31" s="29" t="s">
         <v>1112</v>
       </c>
-      <c r="G31" s="29" t="s">
-        <v>1113</v>
-      </c>
       <c r="H31" s="29" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="I31" s="29">
         <v>25</v>
       </c>
       <c r="J31" s="29" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="29"/>
@@ -21954,7 +22533,7 @@
       <c r="N31" s="29"/>
       <c r="O31" s="29"/>
       <c r="P31" s="29" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="Q31" s="29" t="s">
         <v>571</v>
@@ -21987,13 +22566,13 @@
         <v>564</v>
       </c>
       <c r="AA31" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AB31" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AC31" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="AD31" s="6">
         <v>29500</v>
@@ -22014,22 +22593,22 @@
         <v>8874</v>
       </c>
       <c r="E32" s="5" t="s">
+        <v>961</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>961</v>
+      </c>
+      <c r="G32" s="29" t="s">
         <v>962</v>
       </c>
-      <c r="F32" s="5" t="s">
-        <v>962</v>
-      </c>
-      <c r="G32" s="29" t="s">
+      <c r="H32" s="29" t="s">
         <v>963</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>964</v>
       </c>
       <c r="I32" s="29">
         <v>20</v>
       </c>
       <c r="J32" s="29" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="29"/>
@@ -22037,7 +22616,7 @@
       <c r="N32" s="29"/>
       <c r="O32" s="29"/>
       <c r="P32" s="29" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q32" s="29" t="s">
         <v>571</v>
@@ -22049,7 +22628,7 @@
         <v>569</v>
       </c>
       <c r="T32" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U32" s="29" t="s">
         <v>591</v>
@@ -22058,7 +22637,7 @@
         <v>714</v>
       </c>
       <c r="W32" s="5" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="X32" s="5" t="s">
         <v>667</v>
@@ -22067,25 +22646,25 @@
         <v>607</v>
       </c>
       <c r="Z32" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AA32" s="5" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="AB32" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AC32" s="5" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AD32" s="6">
         <v>50000</v>
       </c>
       <c r="AE32" s="7" t="s">
+        <v>966</v>
+      </c>
+      <c r="AF32" s="7" t="s">
         <v>967</v>
-      </c>
-      <c r="AF32" s="7" t="s">
-        <v>968</v>
       </c>
       <c r="AG32" s="8"/>
     </row>
@@ -22109,16 +22688,16 @@
         <v>42</v>
       </c>
       <c r="G33" s="29" t="s">
+        <v>958</v>
+      </c>
+      <c r="H33" s="29" t="s">
         <v>959</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>960</v>
       </c>
       <c r="I33" s="29">
         <v>20</v>
       </c>
       <c r="J33" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="29"/>
@@ -22126,7 +22705,7 @@
       <c r="N33" s="29"/>
       <c r="O33" s="29"/>
       <c r="P33" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q33" s="29" t="s">
         <v>571</v>
@@ -22138,7 +22717,7 @@
         <v>569</v>
       </c>
       <c r="T33" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U33" s="29" t="s">
         <v>591</v>
@@ -22156,13 +22735,13 @@
         <v>607</v>
       </c>
       <c r="Z33" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="AA33" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB33" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AC33" s="5" t="s">
         <v>7</v>
@@ -22198,16 +22777,16 @@
         <v>42</v>
       </c>
       <c r="G34" s="29" t="s">
+        <v>958</v>
+      </c>
+      <c r="H34" s="29" t="s">
         <v>959</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>960</v>
       </c>
       <c r="I34" s="29">
         <v>20</v>
       </c>
       <c r="J34" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="29"/>
@@ -22215,7 +22794,7 @@
       <c r="N34" s="29"/>
       <c r="O34" s="29"/>
       <c r="P34" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q34" s="29" t="s">
         <v>571</v>
@@ -22227,7 +22806,7 @@
         <v>569</v>
       </c>
       <c r="T34" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U34" s="29" t="s">
         <v>591</v>
@@ -22245,13 +22824,13 @@
         <v>607</v>
       </c>
       <c r="Z34" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="AA34" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB34" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AC34" s="5" t="s">
         <v>7</v>
@@ -22283,23 +22862,47 @@
       <c r="E35" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
+      <c r="F35" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>1168</v>
+      </c>
+      <c r="I35" s="29">
+        <v>2.25</v>
+      </c>
+      <c r="J35" s="29" t="s">
+        <v>1169</v>
+      </c>
       <c r="K35" s="5"/>
       <c r="L35" s="29"/>
       <c r="M35" s="29"/>
       <c r="N35" s="29"/>
       <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="29"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
+      <c r="P35" s="29" t="s">
+        <v>1067</v>
+      </c>
+      <c r="Q35" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="R35" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="S35" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T35" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U35" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V35" s="29" t="s">
+        <v>763</v>
+      </c>
       <c r="W35" s="5" t="s">
         <v>242</v>
       </c>
@@ -22309,9 +22912,15 @@
       <c r="Y35" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z35" s="5"/>
-      <c r="AA35" s="5"/>
-      <c r="AB35" s="5"/>
+      <c r="Z35" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="AA35" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="AB35" s="5" t="s">
+        <v>1167</v>
+      </c>
       <c r="AC35" s="5" t="s">
         <v>21</v>
       </c>
@@ -22343,19 +22952,19 @@
         <v>289</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>1037</v>
+        <v>1153</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I36" s="29">
         <v>21.7</v>
       </c>
       <c r="J36" s="29" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="29"/>
@@ -22363,7 +22972,7 @@
       <c r="N36" s="29"/>
       <c r="O36" s="29"/>
       <c r="P36" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q36" s="29" t="s">
         <v>571</v>
@@ -22375,7 +22984,7 @@
         <v>571</v>
       </c>
       <c r="T36" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U36" s="29" t="s">
         <v>591</v>
@@ -22393,13 +23002,13 @@
         <v>607</v>
       </c>
       <c r="Z36" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AA36" s="5" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AB36" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AC36" s="5" t="s">
         <v>347</v>
@@ -22414,6 +23023,9 @@
         <v>349</v>
       </c>
       <c r="AG36" s="8"/>
+      <c r="AI36" s="1" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="37" spans="1:36" s="1" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
@@ -22432,19 +23044,19 @@
         <v>289</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I37" s="29">
         <v>21.7</v>
       </c>
       <c r="J37" s="29" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="29"/>
@@ -22452,7 +23064,7 @@
       <c r="N37" s="29"/>
       <c r="O37" s="29"/>
       <c r="P37" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q37" s="29" t="s">
         <v>571</v>
@@ -22464,7 +23076,7 @@
         <v>571</v>
       </c>
       <c r="T37" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U37" s="29" t="s">
         <v>591</v>
@@ -22482,13 +23094,13 @@
         <v>607</v>
       </c>
       <c r="Z37" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AA37" s="5" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AB37" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AC37" s="5" t="s">
         <v>347</v>
@@ -22521,19 +23133,19 @@
         <v>289</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I38" s="29">
         <v>21.7</v>
       </c>
       <c r="J38" s="29" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="29"/>
@@ -22541,7 +23153,7 @@
       <c r="N38" s="29"/>
       <c r="O38" s="29"/>
       <c r="P38" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q38" s="29" t="s">
         <v>571</v>
@@ -22553,7 +23165,7 @@
         <v>571</v>
       </c>
       <c r="T38" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U38" s="29" t="s">
         <v>591</v>
@@ -22571,13 +23183,13 @@
         <v>607</v>
       </c>
       <c r="Z38" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AA38" s="5" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="AB38" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AC38" s="5" t="s">
         <v>122</v>
@@ -22610,40 +23222,40 @@
         <v>284</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G39" s="29" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H39" s="29" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I39" s="29">
         <v>4.8</v>
       </c>
       <c r="J39" s="29" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L39" s="29" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M39" s="29" t="s">
         <v>1044</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>1036</v>
-      </c>
-      <c r="L39" s="29" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M39" s="29" t="s">
-        <v>1045</v>
       </c>
       <c r="N39" s="29">
         <v>40</v>
       </c>
       <c r="O39" s="29" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P39" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q39" s="29" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="R39" s="29" t="s">
         <v>569</v>
@@ -22652,7 +23264,7 @@
         <v>571</v>
       </c>
       <c r="T39" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U39" s="29" t="s">
         <v>591</v>
@@ -22670,13 +23282,13 @@
         <v>607</v>
       </c>
       <c r="Z39" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AA39" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB39" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AC39" s="5" t="s">
         <v>21</v>
@@ -22709,40 +23321,40 @@
         <v>284</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G40" s="29" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H40" s="29" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I40" s="29">
         <v>4.8</v>
       </c>
       <c r="J40" s="29" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L40" s="29" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M40" s="29" t="s">
         <v>1044</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>1036</v>
-      </c>
-      <c r="L40" s="29" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M40" s="29" t="s">
-        <v>1045</v>
       </c>
       <c r="N40" s="29">
         <v>40</v>
       </c>
       <c r="O40" s="29" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P40" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q40" s="29" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="R40" s="29" t="s">
         <v>569</v>
@@ -22751,7 +23363,7 @@
         <v>571</v>
       </c>
       <c r="T40" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U40" s="29" t="s">
         <v>591</v>
@@ -22769,13 +23381,13 @@
         <v>607</v>
       </c>
       <c r="Z40" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AA40" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB40" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AC40" s="5" t="s">
         <v>21</v>
@@ -22808,40 +23420,40 @@
         <v>284</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G41" s="29" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H41" s="29" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I41" s="29">
         <v>4.8</v>
       </c>
       <c r="J41" s="29" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L41" s="29" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M41" s="29" t="s">
         <v>1044</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>1036</v>
-      </c>
-      <c r="L41" s="29" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M41" s="29" t="s">
-        <v>1045</v>
       </c>
       <c r="N41" s="29">
         <v>40</v>
       </c>
       <c r="O41" s="29" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P41" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q41" s="29" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="R41" s="29" t="s">
         <v>569</v>
@@ -22850,7 +23462,7 @@
         <v>571</v>
       </c>
       <c r="T41" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U41" s="29" t="s">
         <v>591</v>
@@ -22868,13 +23480,13 @@
         <v>607</v>
       </c>
       <c r="Z41" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AA41" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB41" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AC41" s="5" t="s">
         <v>21</v>
@@ -22890,10 +23502,10 @@
       </c>
       <c r="AG41" s="8"/>
       <c r="AI41" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="AJ41" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="42" spans="1:36" s="1" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -22913,40 +23525,40 @@
         <v>284</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G42" s="29" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H42" s="29" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I42" s="29">
         <v>4.8</v>
       </c>
       <c r="J42" s="29" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L42" s="29" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M42" s="29" t="s">
         <v>1044</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>1036</v>
-      </c>
-      <c r="L42" s="29" t="s">
-        <v>1039</v>
-      </c>
-      <c r="M42" s="29" t="s">
-        <v>1045</v>
       </c>
       <c r="N42" s="29">
         <v>40</v>
       </c>
       <c r="O42" s="29" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P42" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q42" s="29" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="R42" s="29" t="s">
         <v>569</v>
@@ -22955,7 +23567,7 @@
         <v>571</v>
       </c>
       <c r="T42" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U42" s="29" t="s">
         <v>591</v>
@@ -22973,13 +23585,13 @@
         <v>607</v>
       </c>
       <c r="Z42" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="AA42" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB42" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="AC42" s="5" t="s">
         <v>21</v>
@@ -22995,10 +23607,10 @@
       </c>
       <c r="AG42" s="8"/>
       <c r="AI42" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="AJ42" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="43" spans="1:36" s="1" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -23018,40 +23630,40 @@
         <v>351</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G43" s="29" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H43" s="29" t="s">
         <v>1124</v>
-      </c>
-      <c r="H43" s="29" t="s">
-        <v>1125</v>
       </c>
       <c r="I43" s="29">
         <v>12</v>
       </c>
       <c r="J43" s="29" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="L43" s="29" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="M43" s="29" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="N43" s="29">
         <v>9</v>
       </c>
       <c r="O43" s="29" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="P43" s="29" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="Q43" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="R43" s="29" t="s">
         <v>569</v>
@@ -23060,7 +23672,7 @@
         <v>571</v>
       </c>
       <c r="T43" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U43" s="29" t="s">
         <v>591</v>
@@ -23078,13 +23690,13 @@
         <v>607</v>
       </c>
       <c r="Z43" s="5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="AA43" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB43" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AC43" s="5" t="s">
         <v>122</v>
@@ -23117,40 +23729,40 @@
         <v>355</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="G44" s="29" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H44" s="29" t="s">
         <v>1026</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>1027</v>
       </c>
       <c r="I44" s="29">
         <v>5</v>
       </c>
       <c r="J44" s="29" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L44" s="29" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="M44" s="29" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="N44" s="29">
         <v>50</v>
       </c>
       <c r="O44" s="29" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P44" s="29" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q44" s="29" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="R44" s="29" t="s">
         <v>569</v>
@@ -23159,7 +23771,7 @@
         <v>569</v>
       </c>
       <c r="T44" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U44" s="29" t="s">
         <v>591</v>
@@ -23177,13 +23789,13 @@
         <v>607</v>
       </c>
       <c r="Z44" s="5" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AA44" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB44" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AC44" s="5" t="s">
         <v>21</v>
@@ -23215,23 +23827,47 @@
       <c r="E45" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="F45" s="5"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
+      <c r="F45" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>1163</v>
+      </c>
+      <c r="I45" s="29">
+        <v>20</v>
+      </c>
+      <c r="J45" s="29" t="s">
+        <v>1164</v>
+      </c>
       <c r="K45" s="5"/>
       <c r="L45" s="29"/>
       <c r="M45" s="29"/>
       <c r="N45" s="29"/>
       <c r="O45" s="29"/>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="29"/>
-      <c r="R45" s="29"/>
-      <c r="S45" s="29"/>
-      <c r="T45" s="29"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="29"/>
+      <c r="P45" s="29" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q45" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="R45" s="29" t="s">
+        <v>569</v>
+      </c>
+      <c r="S45" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T45" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U45" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V45" s="29" t="s">
+        <v>576</v>
+      </c>
       <c r="W45" s="5" t="s">
         <v>242</v>
       </c>
@@ -23241,9 +23877,15 @@
       <c r="Y45" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z45" s="5"/>
-      <c r="AA45" s="5"/>
-      <c r="AB45" s="5"/>
+      <c r="Z45" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AA45" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="AB45" s="5" t="s">
+        <v>1143</v>
+      </c>
       <c r="AC45" s="5" t="s">
         <v>7</v>
       </c>
@@ -23273,40 +23915,40 @@
         <v>359</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H46" s="29" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="I46" s="29">
         <v>20</v>
       </c>
       <c r="J46" s="29" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="L46" s="29" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="M46" s="29" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="N46" s="29">
         <v>2</v>
       </c>
       <c r="O46" s="29" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="P46" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q46" s="29" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="R46" s="29" t="s">
         <v>571</v>
@@ -23315,7 +23957,7 @@
         <v>571</v>
       </c>
       <c r="T46" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U46" s="29" t="s">
         <v>591</v>
@@ -23333,13 +23975,13 @@
         <v>607</v>
       </c>
       <c r="Z46" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="AA46" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB46" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AC46" s="5" t="s">
         <v>7</v>
@@ -23370,19 +24012,19 @@
         <v>289</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G47" s="29" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H47" s="29" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I47" s="29">
         <v>22.9</v>
       </c>
       <c r="J47" s="29" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="29"/>
@@ -23390,7 +24032,7 @@
       <c r="N47" s="29"/>
       <c r="O47" s="29"/>
       <c r="P47" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q47" s="29" t="s">
         <v>571</v>
@@ -23402,7 +24044,7 @@
         <v>569</v>
       </c>
       <c r="T47" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U47" s="29" t="s">
         <v>615</v>
@@ -23426,7 +24068,7 @@
         <v>679</v>
       </c>
       <c r="AB47" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AC47" s="5" t="s">
         <v>7</v>
@@ -23459,19 +24101,19 @@
         <v>289</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G48" s="29" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H48" s="29" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="I48" s="29">
         <v>22.9</v>
       </c>
       <c r="J48" s="29" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="29"/>
@@ -23479,7 +24121,7 @@
       <c r="N48" s="29"/>
       <c r="O48" s="29"/>
       <c r="P48" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q48" s="29" t="s">
         <v>571</v>
@@ -23491,7 +24133,7 @@
         <v>569</v>
       </c>
       <c r="T48" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U48" s="29" t="s">
         <v>615</v>
@@ -23515,7 +24157,7 @@
         <v>679</v>
       </c>
       <c r="AB48" s="5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AC48" s="5" t="s">
         <v>7</v>
@@ -23548,40 +24190,40 @@
         <v>443</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G49" s="29" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H49" s="29" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="I49" s="29">
         <v>18.2</v>
       </c>
       <c r="J49" s="29" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="L49" s="29" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="M49" s="29" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N49" s="29">
         <v>9.1</v>
       </c>
       <c r="O49" s="29" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="P49" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q49" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="R49" s="29" t="s">
         <v>569</v>
@@ -23590,7 +24232,7 @@
         <v>569</v>
       </c>
       <c r="T49" s="29" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="U49" s="29" t="s">
         <v>591</v>
@@ -23608,13 +24250,13 @@
         <v>607</v>
       </c>
       <c r="Z49" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AA49" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB49" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AC49" s="5" t="s">
         <v>7</v>
@@ -23647,19 +24289,19 @@
         <v>362</v>
       </c>
       <c r="F50" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G50" s="29" t="s">
         <v>1004</v>
       </c>
-      <c r="G50" s="29" t="s">
+      <c r="H50" s="29" t="s">
         <v>1005</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>1006</v>
       </c>
       <c r="I50" s="29">
         <v>10</v>
       </c>
       <c r="J50" s="29" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="29"/>
@@ -23667,7 +24309,7 @@
       <c r="N50" s="29"/>
       <c r="O50" s="29"/>
       <c r="P50" s="29" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="Q50" s="29" t="s">
         <v>571</v>
@@ -23679,7 +24321,7 @@
         <v>569</v>
       </c>
       <c r="T50" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U50" s="29" t="s">
         <v>591</v>
@@ -23697,13 +24339,13 @@
         <v>607</v>
       </c>
       <c r="Z50" s="5" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="AA50" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB50" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AC50" s="5" t="s">
         <v>15</v>
@@ -23736,19 +24378,19 @@
         <v>42</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G51" s="29" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H51" s="29" t="s">
         <v>1129</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>1130</v>
       </c>
       <c r="I51" s="29">
         <v>36</v>
       </c>
       <c r="J51" s="29" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="29"/>
@@ -23756,7 +24398,7 @@
       <c r="N51" s="29"/>
       <c r="O51" s="29"/>
       <c r="P51" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q51" s="29" t="s">
         <v>571</v>
@@ -23768,13 +24410,13 @@
         <v>571</v>
       </c>
       <c r="T51" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U51" s="29" t="s">
         <v>591</v>
       </c>
       <c r="V51" s="29" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="W51" s="5" t="s">
         <v>295</v>
@@ -23786,13 +24428,13 @@
         <v>607</v>
       </c>
       <c r="Z51" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AA51" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB51" s="5" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="AC51" s="5" t="s">
         <v>7</v>
@@ -23821,19 +24463,19 @@
         <v>42</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G52" s="29" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H52" s="29" t="s">
         <v>1129</v>
-      </c>
-      <c r="H52" s="29" t="s">
-        <v>1130</v>
       </c>
       <c r="I52" s="29">
         <v>36</v>
       </c>
       <c r="J52" s="29" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="29"/>
@@ -23841,7 +24483,7 @@
       <c r="N52" s="29"/>
       <c r="O52" s="29"/>
       <c r="P52" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q52" s="29" t="s">
         <v>571</v>
@@ -23853,13 +24495,13 @@
         <v>571</v>
       </c>
       <c r="T52" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U52" s="29" t="s">
         <v>591</v>
       </c>
       <c r="V52" s="29" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="W52" s="5" t="s">
         <v>295</v>
@@ -23871,13 +24513,13 @@
         <v>607</v>
       </c>
       <c r="Z52" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AA52" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB52" s="5" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="AC52" s="5" t="s">
         <v>7</v>
@@ -23906,19 +24548,19 @@
         <v>42</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G53" s="29" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H53" s="29" t="s">
         <v>1129</v>
-      </c>
-      <c r="H53" s="29" t="s">
-        <v>1130</v>
       </c>
       <c r="I53" s="29">
         <v>36</v>
       </c>
       <c r="J53" s="29" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="29"/>
@@ -23926,7 +24568,7 @@
       <c r="N53" s="29"/>
       <c r="O53" s="29"/>
       <c r="P53" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q53" s="29" t="s">
         <v>571</v>
@@ -23938,13 +24580,13 @@
         <v>571</v>
       </c>
       <c r="T53" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U53" s="29" t="s">
         <v>591</v>
       </c>
       <c r="V53" s="29" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="W53" s="5" t="s">
         <v>295</v>
@@ -23956,13 +24598,13 @@
         <v>607</v>
       </c>
       <c r="Z53" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AA53" s="5" t="s">
         <v>679</v>
       </c>
       <c r="AB53" s="5" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="AC53" s="5" t="s">
         <v>7</v>
@@ -23991,19 +24633,19 @@
         <v>366</v>
       </c>
       <c r="F54" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G54" s="29" t="s">
         <v>1047</v>
       </c>
-      <c r="G54" s="29" t="s">
+      <c r="H54" s="29" t="s">
         <v>1048</v>
-      </c>
-      <c r="H54" s="29" t="s">
-        <v>1049</v>
       </c>
       <c r="I54" s="29">
         <v>15</v>
       </c>
       <c r="J54" s="29" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="29"/>
@@ -24011,7 +24653,7 @@
       <c r="N54" s="29"/>
       <c r="O54" s="29"/>
       <c r="P54" s="29" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Q54" s="29" t="s">
         <v>571</v>
@@ -24023,13 +24665,13 @@
         <v>571</v>
       </c>
       <c r="T54" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U54" s="29" t="s">
         <v>591</v>
       </c>
       <c r="V54" s="29" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="W54" s="5" t="s">
         <v>11</v>
@@ -24041,13 +24683,13 @@
         <v>607</v>
       </c>
       <c r="Z54" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="AA54" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="AB54" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="AC54" s="5" t="s">
         <v>21</v>
@@ -24080,40 +24722,40 @@
         <v>443</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G55" s="29" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H55" s="29" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="I55" s="29">
         <v>9</v>
       </c>
       <c r="J55" s="29" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="L55" s="29" t="s">
+        <v>1001</v>
+      </c>
+      <c r="M55" s="29" t="s">
         <v>1002</v>
-      </c>
-      <c r="M55" s="29" t="s">
-        <v>1003</v>
       </c>
       <c r="N55" s="29">
         <v>17</v>
       </c>
       <c r="O55" s="29" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="P55" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q55" s="29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="R55" s="29" t="s">
         <v>571</v>
@@ -24122,7 +24764,7 @@
         <v>571</v>
       </c>
       <c r="T55" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U55" s="29" t="s">
         <v>591</v>
@@ -24146,7 +24788,7 @@
         <v>679</v>
       </c>
       <c r="AB55" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="AC55" s="5" t="s">
         <v>7</v>
@@ -24178,23 +24820,47 @@
       <c r="E56" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F56" s="5"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="29"/>
+      <c r="F56" s="5" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H56" s="29" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I56" s="29">
+        <v>30</v>
+      </c>
+      <c r="J56" s="29" t="s">
+        <v>1218</v>
+      </c>
       <c r="K56" s="5"/>
       <c r="L56" s="29"/>
       <c r="M56" s="29"/>
       <c r="N56" s="29"/>
       <c r="O56" s="29"/>
-      <c r="P56" s="29"/>
-      <c r="Q56" s="29"/>
-      <c r="R56" s="29"/>
-      <c r="S56" s="29"/>
-      <c r="T56" s="29"/>
-      <c r="U56" s="29"/>
-      <c r="V56" s="29"/>
+      <c r="P56" s="29" t="s">
+        <v>938</v>
+      </c>
+      <c r="Q56" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="R56" s="29" t="s">
+        <v>569</v>
+      </c>
+      <c r="S56" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T56" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U56" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V56" s="29" t="s">
+        <v>763</v>
+      </c>
       <c r="W56" s="5" t="s">
         <v>31</v>
       </c>
@@ -24204,9 +24870,15 @@
       <c r="Y56" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z56" s="5"/>
-      <c r="AA56" s="5"/>
-      <c r="AB56" s="5"/>
+      <c r="Z56" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA56" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="AB56" s="5" t="s">
+        <v>1216</v>
+      </c>
       <c r="AC56" s="5" t="s">
         <v>192</v>
       </c>
@@ -24228,7 +24900,7 @@
       <c r="B57" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C57" s="33" t="s">
+      <c r="C57" s="52" t="s">
         <v>296</v>
       </c>
       <c r="D57" s="41"/>
@@ -24279,7 +24951,7 @@
       <c r="B58" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C58" s="33" t="s">
+      <c r="C58" s="52" t="s">
         <v>296</v>
       </c>
       <c r="D58" s="41"/>
@@ -24335,23 +25007,47 @@
       <c r="E59" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="F59" s="5"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="29"/>
-      <c r="J59" s="29"/>
+      <c r="F59" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H59" s="29" t="s">
+        <v>1191</v>
+      </c>
+      <c r="I59" s="29">
+        <v>25</v>
+      </c>
+      <c r="J59" s="29" t="s">
+        <v>1192</v>
+      </c>
       <c r="K59" s="5"/>
       <c r="L59" s="29"/>
       <c r="M59" s="29"/>
       <c r="N59" s="29"/>
       <c r="O59" s="29"/>
-      <c r="P59" s="29"/>
-      <c r="Q59" s="29"/>
-      <c r="R59" s="29"/>
-      <c r="S59" s="29"/>
-      <c r="T59" s="29"/>
-      <c r="U59" s="29"/>
-      <c r="V59" s="29"/>
+      <c r="P59" s="29" t="s">
+        <v>1067</v>
+      </c>
+      <c r="Q59" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="R59" s="29" t="s">
+        <v>569</v>
+      </c>
+      <c r="S59" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T59" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U59" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V59" s="29" t="s">
+        <v>576</v>
+      </c>
       <c r="W59" s="5" t="s">
         <v>316</v>
       </c>
@@ -24361,9 +25057,15 @@
       <c r="Y59" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z59" s="5"/>
-      <c r="AA59" s="5"/>
-      <c r="AB59" s="5"/>
+      <c r="Z59" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="AA59" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="AB59" s="5" t="s">
+        <v>1172</v>
+      </c>
       <c r="AC59" s="5" t="s">
         <v>122</v>
       </c>
@@ -24396,23 +25098,57 @@
       <c r="E60" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="F60" s="5"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
-      <c r="N60" s="29"/>
-      <c r="O60" s="29"/>
-      <c r="P60" s="29"/>
-      <c r="Q60" s="29"/>
-      <c r="R60" s="29"/>
-      <c r="S60" s="29"/>
-      <c r="T60" s="29"/>
-      <c r="U60" s="29"/>
-      <c r="V60" s="29"/>
+      <c r="F60" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G60" s="29" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H60" s="29" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I60" s="29">
+        <v>35</v>
+      </c>
+      <c r="J60" s="29" t="s">
+        <v>1184</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="L60" s="29" t="s">
+        <v>1190</v>
+      </c>
+      <c r="M60" s="29" t="s">
+        <v>1191</v>
+      </c>
+      <c r="N60" s="29">
+        <v>15</v>
+      </c>
+      <c r="O60" s="29" t="s">
+        <v>1193</v>
+      </c>
+      <c r="P60" s="29" t="s">
+        <v>972</v>
+      </c>
+      <c r="Q60" s="29" t="s">
+        <v>1067</v>
+      </c>
+      <c r="R60" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="S60" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T60" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U60" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V60" s="29" t="s">
+        <v>631</v>
+      </c>
       <c r="W60" s="5" t="s">
         <v>316</v>
       </c>
@@ -24422,9 +25158,15 @@
       <c r="Y60" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z60" s="5"/>
-      <c r="AA60" s="5"/>
-      <c r="AB60" s="5"/>
+      <c r="Z60" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="AA60" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="AB60" s="5" t="s">
+        <v>1194</v>
+      </c>
       <c r="AC60" s="5" t="s">
         <v>347</v>
       </c>
@@ -24457,23 +25199,47 @@
       <c r="E61" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="F61" s="5"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
+      <c r="F61" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G61" s="29" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H61" s="29" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I61" s="29">
+        <v>10</v>
+      </c>
+      <c r="J61" s="29" t="s">
+        <v>1169</v>
+      </c>
       <c r="K61" s="5"/>
       <c r="L61" s="29"/>
       <c r="M61" s="29"/>
       <c r="N61" s="29"/>
       <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
+      <c r="P61" s="29" t="s">
+        <v>1067</v>
+      </c>
+      <c r="Q61" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="R61" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="S61" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T61" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U61" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V61" s="29" t="s">
+        <v>593</v>
+      </c>
       <c r="W61" s="5" t="s">
         <v>242</v>
       </c>
@@ -24483,9 +25249,15 @@
       <c r="Y61" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z61" s="5"/>
-      <c r="AA61" s="5"/>
-      <c r="AB61" s="5"/>
+      <c r="Z61" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA61" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="AB61" s="5" t="s">
+        <v>1221</v>
+      </c>
       <c r="AC61" s="5" t="s">
         <v>302</v>
       </c>
@@ -24518,23 +25290,47 @@
       <c r="E62" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="F62" s="5"/>
-      <c r="G62" s="29"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="29"/>
-      <c r="J62" s="29"/>
+      <c r="F62" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="G62" s="29" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H62" s="29" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I62" s="29">
+        <v>10</v>
+      </c>
+      <c r="J62" s="29" t="s">
+        <v>1169</v>
+      </c>
       <c r="K62" s="5"/>
       <c r="L62" s="29"/>
       <c r="M62" s="29"/>
       <c r="N62" s="29"/>
       <c r="O62" s="29"/>
-      <c r="P62" s="29"/>
-      <c r="Q62" s="29"/>
-      <c r="R62" s="29"/>
-      <c r="S62" s="29"/>
-      <c r="T62" s="29"/>
-      <c r="U62" s="29"/>
-      <c r="V62" s="29"/>
+      <c r="P62" s="29" t="s">
+        <v>1067</v>
+      </c>
+      <c r="Q62" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="R62" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="S62" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="T62" s="29" t="s">
+        <v>871</v>
+      </c>
+      <c r="U62" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="V62" s="29" t="s">
+        <v>593</v>
+      </c>
       <c r="W62" s="5" t="s">
         <v>242</v>
       </c>
@@ -24544,9 +25340,15 @@
       <c r="Y62" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Z62" s="5"/>
-      <c r="AA62" s="5"/>
-      <c r="AB62" s="5"/>
+      <c r="Z62" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="AA62" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="AB62" s="5" t="s">
+        <v>1221</v>
+      </c>
       <c r="AC62" s="5" t="s">
         <v>302</v>
       </c>
@@ -24580,19 +25382,19 @@
         <v>378</v>
       </c>
       <c r="F63" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G63" s="29" t="s">
         <v>1118</v>
       </c>
-      <c r="G63" s="29" t="s">
-        <v>1119</v>
-      </c>
       <c r="H63" s="29" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I63" s="29">
         <v>66.5</v>
       </c>
       <c r="J63" s="29" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="29"/>
@@ -24600,7 +25402,7 @@
       <c r="N63" s="29"/>
       <c r="O63" s="29"/>
       <c r="P63" s="29" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="Q63" s="29" t="s">
         <v>571</v>
@@ -24612,7 +25414,7 @@
         <v>571</v>
       </c>
       <c r="T63" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U63" s="29" t="s">
         <v>621</v>
@@ -24630,13 +25432,13 @@
         <v>607</v>
       </c>
       <c r="Z63" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AA63" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AB63" s="5" t="s">
         <v>1062</v>
-      </c>
-      <c r="AA63" s="5" t="s">
-        <v>1121</v>
-      </c>
-      <c r="AB63" s="5" t="s">
-        <v>1063</v>
       </c>
       <c r="AC63" s="5" t="s">
         <v>7</v>
@@ -24667,19 +25469,19 @@
         <v>378</v>
       </c>
       <c r="F64" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G64" s="29" t="s">
         <v>1118</v>
       </c>
-      <c r="G64" s="29" t="s">
-        <v>1119</v>
-      </c>
       <c r="H64" s="29" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I64" s="29">
         <v>66.5</v>
       </c>
       <c r="J64" s="29" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="K64" s="5"/>
       <c r="L64" s="29"/>
@@ -24687,7 +25489,7 @@
       <c r="N64" s="29"/>
       <c r="O64" s="29"/>
       <c r="P64" s="29" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="Q64" s="29" t="s">
         <v>571</v>
@@ -24699,7 +25501,7 @@
         <v>571</v>
       </c>
       <c r="T64" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U64" s="29" t="s">
         <v>621</v>
@@ -24717,13 +25519,13 @@
         <v>607</v>
       </c>
       <c r="Z64" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AA64" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AB64" s="5" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="AC64" s="5" t="s">
         <v>21</v>
@@ -24754,40 +25556,40 @@
         <v>406</v>
       </c>
       <c r="F65" s="18" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G65" s="32" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H65" s="62" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="I65" s="32">
         <v>15</v>
       </c>
       <c r="J65" s="32" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="K65" s="18" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="L65" s="32" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="M65" s="32" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="N65" s="32">
         <v>8</v>
       </c>
       <c r="O65" s="32" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="P65" s="32" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q65" s="32" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="R65" s="32" t="s">
         <v>569</v>
@@ -24796,7 +25598,7 @@
         <v>569</v>
       </c>
       <c r="T65" s="32" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U65" s="32" t="s">
         <v>591</v>
@@ -24814,13 +25616,13 @@
         <v>607</v>
       </c>
       <c r="Z65" s="18" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AA65" s="18" t="s">
         <v>679</v>
       </c>
       <c r="AB65" s="18" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AC65" s="18" t="s">
         <v>122</v>
@@ -24855,40 +25657,40 @@
         <v>457</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G66" s="29" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H66" s="29" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="I66" s="29">
         <v>3.5</v>
       </c>
       <c r="J66" s="29" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="L66" s="29" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="M66" s="29" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="N66" s="29">
         <v>1</v>
       </c>
       <c r="O66" s="29" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="P66" s="29" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="Q66" s="29" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="R66" s="29" t="s">
         <v>569</v>
@@ -24897,7 +25699,7 @@
         <v>569</v>
       </c>
       <c r="T66" s="29" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="U66" s="29" t="s">
         <v>591</v>
@@ -24915,13 +25717,13 @@
         <v>607</v>
       </c>
       <c r="Z66" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AA66" s="5" t="s">
         <v>688</v>
       </c>
       <c r="AB66" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="AC66" s="5" t="s">
         <v>122</v>
@@ -25108,7 +25910,7 @@
         <v>612</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G3" s="22" t="s">
         <v>628</v>
@@ -25323,7 +26125,7 @@
         <v>623</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L12" s="48"/>
       <c r="W12" s="5" t="s">
@@ -25343,7 +26145,7 @@
         <v>624</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="L13" s="50" t="s">
         <v>641</v>
@@ -25415,16 +26217,16 @@
     </row>
     <row r="18" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C18" s="59" t="s">
+        <v>875</v>
+      </c>
+      <c r="D18" s="59" t="s">
         <v>876</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="E18" s="59" t="s">
         <v>877</v>
       </c>
-      <c r="E18" s="59" t="s">
-        <v>878</v>
-      </c>
       <c r="F18" s="59" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G18" s="22"/>
       <c r="W18" s="5" t="s">
@@ -25438,7 +26240,7 @@
       <c r="C19" s="59"/>
       <c r="D19" s="59"/>
       <c r="E19" s="59" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="F19" s="59"/>
       <c r="L19" s="44" t="s">
@@ -25453,16 +26255,16 @@
     </row>
     <row r="20" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="59" t="s">
+        <v>878</v>
+      </c>
+      <c r="D20" s="59" t="s">
         <v>879</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="E20" s="60" t="s">
+        <v>917</v>
+      </c>
+      <c r="F20" s="59" t="s">
         <v>880</v>
-      </c>
-      <c r="E20" s="60" t="s">
-        <v>918</v>
-      </c>
-      <c r="F20" s="59" t="s">
-        <v>881</v>
       </c>
       <c r="L20" s="48"/>
       <c r="W20" s="5" t="s">
@@ -25474,16 +26276,16 @@
     </row>
     <row r="21" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" s="59" t="s">
+        <v>881</v>
+      </c>
+      <c r="D21" s="59" t="s">
         <v>882</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="E21" s="60" t="s">
+        <v>918</v>
+      </c>
+      <c r="F21" s="59" t="s">
         <v>883</v>
-      </c>
-      <c r="E21" s="60" t="s">
-        <v>919</v>
-      </c>
-      <c r="F21" s="59" t="s">
-        <v>884</v>
       </c>
       <c r="L21" s="50" t="s">
         <v>645</v>
@@ -25497,16 +26299,16 @@
     </row>
     <row r="22" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C22" s="59" t="s">
+        <v>884</v>
+      </c>
+      <c r="D22" s="59" t="s">
         <v>885</v>
       </c>
-      <c r="D22" s="59" t="s">
+      <c r="E22" s="60" t="s">
+        <v>919</v>
+      </c>
+      <c r="F22" s="59" t="s">
         <v>886</v>
-      </c>
-      <c r="E22" s="60" t="s">
-        <v>920</v>
-      </c>
-      <c r="F22" s="59" t="s">
-        <v>887</v>
       </c>
       <c r="L22" s="48"/>
       <c r="W22" s="5" t="s">
@@ -25518,16 +26320,16 @@
     </row>
     <row r="23" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="59" t="s">
+        <v>887</v>
+      </c>
+      <c r="D23" s="59" t="s">
         <v>888</v>
       </c>
-      <c r="D23" s="59" t="s">
+      <c r="E23" s="59" t="s">
         <v>889</v>
       </c>
-      <c r="E23" s="59" t="s">
-        <v>890</v>
-      </c>
       <c r="F23" s="59" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="L23" s="50" t="s">
         <v>646</v>
@@ -25541,16 +26343,16 @@
     </row>
     <row r="24" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C24" s="59" t="s">
+        <v>890</v>
+      </c>
+      <c r="D24" s="59" t="s">
         <v>891</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="E24" s="60" t="s">
+        <v>920</v>
+      </c>
+      <c r="F24" s="59" t="s">
         <v>892</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>921</v>
-      </c>
-      <c r="F24" s="59" t="s">
-        <v>893</v>
       </c>
       <c r="L24" s="48"/>
       <c r="W24" s="5" t="s">
@@ -25562,16 +26364,16 @@
     </row>
     <row r="25" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="59" t="s">
+        <v>893</v>
+      </c>
+      <c r="D25" s="59" t="s">
         <v>894</v>
       </c>
-      <c r="D25" s="59" t="s">
+      <c r="E25" s="59" t="s">
         <v>895</v>
       </c>
-      <c r="E25" s="59" t="s">
-        <v>896</v>
-      </c>
       <c r="F25" s="59" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L25" s="50" t="s">
         <v>647</v>
@@ -25585,16 +26387,16 @@
     </row>
     <row r="26" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C26" s="59" t="s">
+        <v>896</v>
+      </c>
+      <c r="D26" s="59" t="s">
         <v>897</v>
       </c>
-      <c r="D26" s="59" t="s">
+      <c r="E26" s="60" t="s">
+        <v>921</v>
+      </c>
+      <c r="F26" s="59" t="s">
         <v>898</v>
-      </c>
-      <c r="E26" s="60" t="s">
-        <v>922</v>
-      </c>
-      <c r="F26" s="59" t="s">
-        <v>899</v>
       </c>
       <c r="L26" s="48"/>
       <c r="W26" s="5" t="s">
@@ -25606,16 +26408,16 @@
     </row>
     <row r="27" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C27" s="59" t="s">
+        <v>899</v>
+      </c>
+      <c r="D27" s="59" t="s">
         <v>900</v>
       </c>
-      <c r="D27" s="59" t="s">
+      <c r="E27" s="60" t="s">
+        <v>922</v>
+      </c>
+      <c r="F27" s="59" t="s">
         <v>901</v>
-      </c>
-      <c r="E27" s="60" t="s">
-        <v>923</v>
-      </c>
-      <c r="F27" s="59" t="s">
-        <v>902</v>
       </c>
       <c r="L27" s="50" t="s">
         <v>648</v>
@@ -25629,16 +26431,16 @@
     </row>
     <row r="28" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C28" s="59" t="s">
+        <v>902</v>
+      </c>
+      <c r="D28" s="59" t="s">
         <v>903</v>
       </c>
-      <c r="D28" s="59" t="s">
+      <c r="E28" s="60" t="s">
+        <v>923</v>
+      </c>
+      <c r="F28" s="59" t="s">
         <v>904</v>
-      </c>
-      <c r="E28" s="60" t="s">
-        <v>924</v>
-      </c>
-      <c r="F28" s="59" t="s">
-        <v>905</v>
       </c>
       <c r="L28" s="48"/>
       <c r="W28" s="5" t="s">
@@ -25650,16 +26452,16 @@
     </row>
     <row r="29" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C29" s="59" t="s">
+        <v>905</v>
+      </c>
+      <c r="D29" s="59" t="s">
         <v>906</v>
       </c>
-      <c r="D29" s="59" t="s">
+      <c r="E29" s="60" t="s">
+        <v>924</v>
+      </c>
+      <c r="F29" s="59" t="s">
         <v>907</v>
-      </c>
-      <c r="E29" s="60" t="s">
-        <v>925</v>
-      </c>
-      <c r="F29" s="59" t="s">
-        <v>908</v>
       </c>
       <c r="L29" s="50" t="s">
         <v>649</v>
@@ -25673,16 +26475,16 @@
     </row>
     <row r="30" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C30" s="59" t="s">
+        <v>908</v>
+      </c>
+      <c r="D30" s="59" t="s">
         <v>909</v>
       </c>
-      <c r="D30" s="59" t="s">
+      <c r="E30" s="60" t="s">
+        <v>925</v>
+      </c>
+      <c r="F30" s="59" t="s">
         <v>910</v>
-      </c>
-      <c r="E30" s="60" t="s">
-        <v>926</v>
-      </c>
-      <c r="F30" s="59" t="s">
-        <v>911</v>
       </c>
       <c r="W30" s="5" t="s">
         <v>47</v>
@@ -25693,16 +26495,16 @@
     </row>
     <row r="31" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="59" t="s">
+        <v>911</v>
+      </c>
+      <c r="D31" s="59" t="s">
         <v>912</v>
       </c>
-      <c r="D31" s="59" t="s">
+      <c r="E31" s="60" t="s">
+        <v>926</v>
+      </c>
+      <c r="F31" s="59" t="s">
         <v>913</v>
-      </c>
-      <c r="E31" s="60" t="s">
-        <v>927</v>
-      </c>
-      <c r="F31" s="59" t="s">
-        <v>914</v>
       </c>
       <c r="W31" s="5" t="s">
         <v>43</v>
@@ -25713,16 +26515,16 @@
     </row>
     <row r="32" spans="3:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="59" t="s">
+        <v>914</v>
+      </c>
+      <c r="D32" s="59" t="s">
         <v>915</v>
       </c>
-      <c r="D32" s="59" t="s">
+      <c r="E32" s="61" t="s">
+        <v>927</v>
+      </c>
+      <c r="F32" s="59" t="s">
         <v>916</v>
-      </c>
-      <c r="E32" s="61" t="s">
-        <v>928</v>
-      </c>
-      <c r="F32" s="59" t="s">
-        <v>917</v>
       </c>
       <c r="W32" s="5" t="s">
         <v>47</v>
